--- a/rules/CORE-000238/positive/01/data/unit-test-coreid-CG0147-positive 1.xlsx
+++ b/rules/CORE-000238/positive/01/data/unit-test-coreid-CG0147-positive 1.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,6 +1146,116 @@
         </is>
       </c>
       <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-OK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2012-11-30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2013-01-23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2014-01-20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>84</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -1162,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5824,6 +5934,164 @@
         <v>55</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-OK</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>54</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2014-01-05</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-OK</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>54</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2014-01-20</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rules/CORE-000238/positive/01/data/unit-test-coreid-CG0147-positive 1.xlsx
+++ b/rules/CORE-000238/positive/01/data/unit-test-coreid-CG0147-positive 1.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,6 +1256,116 @@
         </is>
       </c>
       <c r="Z6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-TIME</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2012-11-30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2013-01-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2014-01-20T10:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>84</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -1272,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6092,6 +6202,164 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-TIME</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>54</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2014-01-05</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-TIME</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>54</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2014-01-20</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
